--- a/server/excel/release/login-7day.xlsx
+++ b/server/excel/release/login-7day.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">3:100001:300#3:100022:50#0:0:2000000#0:4:2000000</t>
   </si>
   <si>
-    <t xml:space="preserve">Ngao Bính, Nguyên bảo, tiến giai thạch, tướng kinh nghiệm</t>
+    <t xml:space="preserve">Ngao Bính, Kim cương, tiến giai thạch, tướng kinh nghiệm</t>
   </si>
   <si>
     <t xml:space="preserve">进阶石*500，元宝*120，金币，英雄经验</t>
@@ -120,7 +120,7 @@
     <t xml:space="preserve">3:100004:1000#3:100022:50#0:0:7000000#0:4:7000000</t>
   </si>
   <si>
-    <t xml:space="preserve">Đấu chiến thánh Phật, Nguyên bảo, tiến giai thạch, cao cấp tầm bảo quyển</t>
+    <t xml:space="preserve">Đấu chiến thánh Phật, Kim cương, tiến giai thạch, cao cấp tầm bảo quyển</t>
   </si>
   <si>
     <t xml:space="preserve">鎏金粉*1000，元宝*120，金币，英雄经验</t>
